--- a/results/Int Task Remove ACC -0.4/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_1_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6915578824162334</v>
+        <v>0.6991670013190511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7109169195927477</v>
+        <v>0.7056285228989863</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6914007164482092</v>
+        <v>0.7066347661027488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6792936027926393</v>
+        <v>0.702411287907479</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6770540353743446</v>
+        <v>0.6971830905420759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6763064968791601</v>
+        <v>0.693392818905942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6747399808124166</v>
+        <v>0.7023954760585747</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6750558367820945</v>
+        <v>0.6980464555930892</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.678157245217773</v>
+        <v>0.6882834961636264</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6766065409999337</v>
+        <v>0.6857995118520286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6680896695666487</v>
+        <v>0.693865840843644</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6650867518042654</v>
+        <v>0.6818398819788358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6650867518042654</v>
+        <v>0.6608316499111869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6645280029749137</v>
+        <v>0.6597539676310498</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6599488534313998</v>
+        <v>0.6597539676310498</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6470258102715294</v>
+        <v>0.6574858245822053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6413118271867787</v>
+        <v>0.6657980945007532</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6378516993355976</v>
+        <v>0.6657980945007532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6314600927984078</v>
+        <v>0.66622977702626</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6463910502649151</v>
+        <v>0.6472728942236839</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.64426578536882</v>
+        <v>0.6500155832438599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6460593824463331</v>
+        <v>0.6431968662820514</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6585094036685013</v>
+        <v>0.6435984491433788</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6566285556657093</v>
+        <v>0.6399367678447193</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6621108856388025</v>
+        <v>0.6408828117201234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6567826735664749</v>
+        <v>0.6313025458219761</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6535842984911304</v>
+        <v>0.6306994095131703</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6478386917085712</v>
+        <v>0.6327088478534367</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.653639925718601</v>
+        <v>0.633470674163896</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6430391288014161</v>
+        <v>0.6284884177254255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6357473899019056</v>
+        <v>0.6085119564248305</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6352728439305741</v>
+        <v>0.6038297441071335</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6409995907969706</v>
+        <v>0.6009156013036584</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6409710151664206</v>
+        <v>0.6070898425444656</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6409710151664206</v>
+        <v>0.5564233445375206</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6409710151664206</v>
+        <v>0.5552027841046341</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6578445439977079</v>
+        <v>0.5633594120887871</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6595539382172007</v>
+        <v>0.5526029732372074</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6561065741476652</v>
+        <v>0.5577296318620567</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6383313889204278</v>
+        <v>0.5624975710714033</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6125716010049478</v>
+        <v>0.556036049491468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6035230323392315</v>
+        <v>0.556036049491468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5809768598353892</v>
+        <v>0.5458541713181443</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5978774402635969</v>
+        <v>0.5458541713181443</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5978774402635969</v>
+        <v>0.5440447623917269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5984520009418528</v>
+        <v>0.5298853469500658</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5925252246616074</v>
+        <v>0.5019109476669712</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5898922660627429</v>
+        <v>0.502514083975777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6000251846557246</v>
+        <v>0.5063773187219149</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5641084746176009</v>
+        <v>0.5083153179858066</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.549550524381871</v>
+        <v>0.5089184542946125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5422587854823604</v>
+        <v>0.5086025983249347</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5433890469227094</v>
+        <v>0.5044949466854936</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5305599223352463</v>
+        <v>0.5036045300375598</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5345374596035837</v>
+        <v>0.5012062726176115</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5336470429556499</v>
+        <v>0.5021109770808203</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.536619861053854</v>
+        <v>0.5060313630880579</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5318090583986826</v>
+        <v>0.5078407720144753</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5248587030321411</v>
+        <v>0.505729794933655</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5254618393409469</v>
+        <v>0.5072376357056695</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5200479003769697</v>
+        <v>0.5081423401688782</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.510139014727499</v>
+        <v>0.5081423401688782</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5</v>
+        <v>0.5078407720144753</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5</v>
+        <v>0.508443908323281</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5</v>
+        <v>0.5078407720144753</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5006031363088058</v>
+        <v>0.5078407720144753</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5006031363088058</v>
+        <v>0.5066344993968637</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5</v>
+        <v>0.5105548854041013</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5</v>
+        <v>0.5105548854041013</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5</v>
+        <v>0.5105548854041013</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5003015681544029</v>
+        <v>0.502714113389626</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5</v>
+        <v>0.5030013937287541</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5</v>
+        <v>0.5039060981919627</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5</v>
+        <v>0.5081280523536033</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5</v>
+        <v>0.5051266586248492</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5</v>
+        <v>0.5045235223160435</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.5081423401688782</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.5081423401688782</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.5225890359496673</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.5165576728616094</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.5075392038600723</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.5075392038600723</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.5021109770808203</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.5018094089264173</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.5024125452352232</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5009047044632087</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5006031363088058</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5008761288326589</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.5005031216018813</v>
       </c>
     </row>
   </sheetData>
